--- a/data/trans_orig/P37A$medicootras-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicootras-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1025656</t>
+          <t>1024944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1307078</t>
+          <t>1307024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1314158</t>
+          <t>1314157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2335133</t>
+          <t>2336003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2344922</t>
+          <t>2344934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1687790</t>
+          <t>1686539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1579712</t>
+          <t>1579713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1586700</t>
+          <t>1586698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3270218</t>
+          <t>3270624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3279215</t>
+          <t>3279212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1434,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>13535</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4881</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>12198</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541040</t>
+          <t>539802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550495</t>
+          <t>550504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>475176</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>470223</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>476412</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1022939</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1014285</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1026119</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>475176</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>470202</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>476412</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1022939</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1015622</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1026597</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3262086</t>
+          <t>3261851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3273636</t>
+          <t>3273564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3364117</t>
+          <t>3364585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3375962</t>
+          <t>3375959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6630818</t>
+          <t>6630316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6647089</t>
+          <t>6646878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>963967</t>
+          <t>962944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>972777</t>
+          <t>972879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1324872</t>
+          <t>1324775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1335551</t>
+          <t>1335534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2290798</t>
+          <t>2292362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2306465</t>
+          <t>2306806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1943651</t>
+          <t>1944573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1958840</t>
+          <t>1958822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1732768</t>
+          <t>1733190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1748892</t>
+          <t>1749684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3683979</t>
+          <t>3684001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3705649</t>
+          <t>3705854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471565</t>
+          <t>469340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446966</t>
+          <t>447227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457645</t>
+          <t>457636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>925321</t>
+          <t>924163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937879</t>
+          <t>937121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58261</t>
+          <t>58383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3392099</t>
+          <t>3392758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3409836</t>
+          <t>3409970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3515556</t>
+          <t>3514876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3537248</t>
+          <t>3536946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6915751</t>
+          <t>6915629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6943201</t>
+          <t>6944940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>744052</t>
+          <t>744656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>753363</t>
+          <t>753375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>982160</t>
+          <t>981626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>992510</t>
+          <t>992108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1731388</t>
+          <t>1730166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1744039</t>
+          <t>1744164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2054323</t>
+          <t>2055243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2069741</t>
+          <t>2069985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1968642</t>
+          <t>1968819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1982470</t>
+          <t>1982427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4029899</t>
+          <t>4028133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4048901</t>
+          <t>4049462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535902</t>
+          <t>534875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545901</t>
+          <t>545983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535752</t>
+          <t>536125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547290</t>
+          <t>547229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1077953</t>
+          <t>1077033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092224</t>
+          <t>1092362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>31490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>58389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3346023</t>
+          <t>3344958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3364915</t>
+          <t>3364842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3497229</t>
+          <t>3497589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3517519</t>
+          <t>3517529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6850526</t>
+          <t>6851329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6878017</t>
+          <t>6878228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,67 +5537,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7376</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3746</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12341</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6179</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3094</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10553</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>23349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5650,69 +5650,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>508837</t>
+          <t>570928</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>502803</t>
+          <t>564122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>512574</t>
+          <t>575238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>814662</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>809697</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>818292</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>749329</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>744955</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>752414</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1258167</t>
+          <t>1385590</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1250510</t>
+          <t>1377218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1262987</t>
+          <t>1391312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,27 +5880,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37458</t>
+          <t>42153</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>56874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5993,22 +5993,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2279730</t>
+          <t>2219273</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2266943</t>
+          <t>2207902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2285444</t>
+          <t>2224995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2210494</t>
+          <t>2140673</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2200365</t>
+          <t>2129239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2220231</t>
+          <t>2149571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4490224</t>
+          <t>4359947</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4475586</t>
+          <t>4345085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4502243</t>
+          <t>4371035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>642604</t>
+          <t>707438</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637691</t>
+          <t>702248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645356</t>
+          <t>710339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>650171</t>
+          <t>723691</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643023</t>
+          <t>716079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654678</t>
+          <t>728695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1292775</t>
+          <t>1431129</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1284889</t>
+          <t>1423109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298510</t>
+          <t>1437407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,67 +6566,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>14454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>49281</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37814</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>61735</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43800</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32131</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56752</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82637</t>
+          <t>90050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -6679,69 +6679,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3431173</t>
+          <t>3497640</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3417197</t>
+          <t>3485963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3438852</t>
+          <t>3506229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3679026</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3666572</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3690493</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5285</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3609994</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3597042</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3621663</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>8627</t>
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7041167</t>
+          <t>7176666</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7023046</t>
+          <t>7158940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7054551</t>
+          <t>7191329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
